--- a/artfynd/A 25754-2025 artfynd.xlsx
+++ b/artfynd/A 25754-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128759028</v>
       </c>
       <c r="B7" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128753555</v>
       </c>
       <c r="B9" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128758936</v>
       </c>
       <c r="B14" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 25754-2025 artfynd.xlsx
+++ b/artfynd/A 25754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128753672</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128753697</v>
       </c>
       <c r="B3" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128759433</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128757474</v>
       </c>
       <c r="B5" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128759028</v>
       </c>
       <c r="B7" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128753068</v>
       </c>
       <c r="B8" t="n">
-        <v>79090</v>
+        <v>79117</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128753555</v>
       </c>
       <c r="B9" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128752700</v>
       </c>
       <c r="B11" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128758534</v>
       </c>
       <c r="B12" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128757228</v>
       </c>
       <c r="B13" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128758936</v>
       </c>
       <c r="B14" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>128752829</v>
       </c>
       <c r="B15" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25754-2025 artfynd.xlsx
+++ b/artfynd/A 25754-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128759433</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128757474</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128759028</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128753068</v>
       </c>
       <c r="B8" t="n">
-        <v>79117</v>
+        <v>79121</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128753555</v>
       </c>
       <c r="B9" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128752700</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128758936</v>
       </c>
       <c r="B14" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>128752829</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25754-2025 artfynd.xlsx
+++ b/artfynd/A 25754-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128759028</v>
       </c>
       <c r="B7" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128753555</v>
       </c>
       <c r="B9" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128758936</v>
       </c>
       <c r="B14" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 25754-2025 artfynd.xlsx
+++ b/artfynd/A 25754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128753672</v>
       </c>
       <c r="B2" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128753697</v>
       </c>
       <c r="B3" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128759433</v>
       </c>
       <c r="B4" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128757474</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128759028</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128753068</v>
       </c>
       <c r="B8" t="n">
-        <v>79121</v>
+        <v>79125</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128753555</v>
       </c>
       <c r="B9" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128752700</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128758534</v>
       </c>
       <c r="B12" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128757228</v>
       </c>
       <c r="B13" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128758936</v>
       </c>
       <c r="B14" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>128752829</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25754-2025 artfynd.xlsx
+++ b/artfynd/A 25754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128753672</v>
       </c>
       <c r="B2" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128753697</v>
       </c>
       <c r="B3" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128759433</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128757474</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128759028</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128753068</v>
       </c>
       <c r="B8" t="n">
-        <v>79125</v>
+        <v>79030</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128753555</v>
       </c>
       <c r="B9" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128752700</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128758534</v>
       </c>
       <c r="B12" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128757228</v>
       </c>
       <c r="B13" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128758936</v>
       </c>
       <c r="B14" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>128752829</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25754-2025 artfynd.xlsx
+++ b/artfynd/A 25754-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128759028</v>
       </c>
       <c r="B7" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128753555</v>
       </c>
       <c r="B9" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128758936</v>
       </c>
       <c r="B14" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 25754-2025 artfynd.xlsx
+++ b/artfynd/A 25754-2025 artfynd.xlsx
@@ -892,7 +892,7 @@
         <v>128759433</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128757474</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128759028</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128753068</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79036</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128753555</v>
       </c>
       <c r="B9" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128752700</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128758936</v>
       </c>
       <c r="B14" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>128752829</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25754-2025 artfynd.xlsx
+++ b/artfynd/A 25754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128753672</v>
       </c>
       <c r="B2" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128753697</v>
       </c>
       <c r="B3" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128759433</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128757474</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128759028</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128753068</v>
       </c>
       <c r="B8" t="n">
-        <v>79036</v>
+        <v>79040</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128753555</v>
       </c>
       <c r="B9" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128752700</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128758534</v>
       </c>
       <c r="B12" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128757228</v>
       </c>
       <c r="B13" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128758936</v>
       </c>
       <c r="B14" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>128752829</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25754-2025 artfynd.xlsx
+++ b/artfynd/A 25754-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128759028</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128753555</v>
       </c>
       <c r="B9" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128758936</v>
       </c>
       <c r="B14" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 25754-2025 artfynd.xlsx
+++ b/artfynd/A 25754-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128753672</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128753697</v>
       </c>
       <c r="B3" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>128759433</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>128757474</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1218,7 +1218,7 @@
         <v>128759028</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>128753068</v>
       </c>
       <c r="B8" t="n">
-        <v>79040</v>
+        <v>79042</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,7 +1432,7 @@
         <v>128753555</v>
       </c>
       <c r="B9" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>128752700</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1762,7 +1762,7 @@
         <v>128758534</v>
       </c>
       <c r="B12" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>128757228</v>
       </c>
       <c r="B13" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>128758936</v>
       </c>
       <c r="B14" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>128752829</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 25754-2025 artfynd.xlsx
+++ b/artfynd/A 25754-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128753555</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128759028</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,6 +1024,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128757007</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128752700</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128752829</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1330,6 +1360,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128757474</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,6 +1472,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128759433</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1549,6 +1589,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128757228</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1661,6 +1706,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758534</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1768,6 +1818,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128753697</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1875,6 +1930,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128753672</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1987,6 +2047,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128757111</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2099,6 +2164,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128757475</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2206,6 +2276,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128758936</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2313,8 +2388,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128753068</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>